--- a/variables(최종).xlsx
+++ b/variables(최종).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c502c410f1ad430/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c502c410f1ad430/바탕 화면/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B9AE7F9-4763-4C28-8676-203DB7FC0DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{9B9AE7F9-4763-4C28-8676-203DB7FC0DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1186204-97E3-44F4-B4EC-A734ABADD1D9}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{1EFFD572-6CE3-4C25-9F73-616CA1E95787}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{1EFFD572-6CE3-4C25-9F73-616CA1E95787}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,22 +65,13 @@
     <t>Lampung</t>
   </si>
   <si>
-    <t>Kep. Bangka Belitung</t>
-  </si>
-  <si>
     <t>Kepulauan Riau</t>
   </si>
   <si>
-    <t>DKI Jakarta</t>
-  </si>
-  <si>
     <t>Jawa Barat</t>
   </si>
   <si>
     <t>Jawa Tengah</t>
-  </si>
-  <si>
-    <t>DI Yogyakarta</t>
   </si>
   <si>
     <t>Jawa Timur</t>
@@ -157,6 +148,18 @@
   </si>
   <si>
     <t>Poverty_2007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yogyakarta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jakarta Raya</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kepulauan Bangka Belitung</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -253,10 +256,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -581,19 +580,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.6">
@@ -615,7 +614,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5">
         <v>14167</v>
@@ -632,7 +631,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5">
         <v>12729</v>
@@ -664,9 +663,9 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B6" s="5">
         <v>11697</v>
@@ -683,7 +682,7 @@
     </row>
     <row r="7" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>15655</v>
@@ -700,7 +699,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5">
         <v>7930</v>
@@ -734,7 +733,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5">
         <v>16170</v>
@@ -751,7 +750,7 @@
     </row>
     <row r="11" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5">
         <v>37207</v>
@@ -768,7 +767,7 @@
     </row>
     <row r="12" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A12" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5">
         <v>62490</v>
@@ -785,7 +784,7 @@
     </row>
     <row r="13" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B13" s="5">
         <v>13058</v>
@@ -802,7 +801,7 @@
     </row>
     <row r="14" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" s="5">
         <v>9649</v>
@@ -819,7 +818,7 @@
     </row>
     <row r="15" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B15" s="5">
         <v>9584</v>
@@ -836,7 +835,7 @@
     </row>
     <row r="16" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B16" s="5">
         <v>14498</v>
@@ -853,7 +852,7 @@
     </row>
     <row r="17" spans="1:5" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A17" s="4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5">
         <v>11408</v>
@@ -870,7 +869,7 @@
     </row>
     <row r="18" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A18" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="5">
         <v>12166</v>
@@ -904,7 +903,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5">
         <v>4302</v>
@@ -921,7 +920,7 @@
     </row>
     <row r="21" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A21" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5">
         <v>10166</v>
@@ -938,7 +937,7 @@
     </row>
     <row r="22" spans="1:5" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B22" s="5">
         <v>13765</v>
@@ -955,7 +954,7 @@
     </row>
     <row r="23" spans="1:5" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B23" s="5">
         <v>11611</v>
@@ -972,7 +971,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5">
         <v>70119</v>
@@ -989,7 +988,7 @@
     </row>
     <row r="25" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B25" s="5">
         <v>11012</v>
@@ -1023,7 +1022,7 @@
     </row>
     <row r="27" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B27" s="5">
         <v>8996</v>
@@ -1040,7 +1039,7 @@
     </row>
     <row r="28" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B28" s="5">
         <v>8837</v>
@@ -1057,7 +1056,7 @@
     </row>
     <row r="29" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A29" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B29" s="5">
         <v>4958</v>
@@ -1074,7 +1073,7 @@
     </row>
     <row r="30" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A30" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B30" s="5">
         <v>6091</v>
@@ -1091,7 +1090,7 @@
     </row>
     <row r="31" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A31" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B31" s="5">
         <v>4377</v>
